--- a/nr-doc-core-body-structure/ig/StructureDefinition-fr-core-address-insee-code.xlsx
+++ b/nr-doc-core-body-structure/ig/StructureDefinition-fr-core-address-insee-code.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T09:03:50+00:00</t>
+    <t>2026-09-17T13:25:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -349,7 +349,7 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t>extensible</t>
+    <t>required</t>
   </si>
   <si>
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-insee-code|2.2.0</t>
